--- a/output/laminas_comunales/comunal_i_ingr_median_a_2020_arica_y_parinacota.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2020_arica_y_parinacota.xlsx
@@ -427,7 +427,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -436,20 +436,12 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>611716</v>
+          <t>Putre</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -462,14 +454,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>General Lagos</t>
+          <t>Arica</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Putre</t>
+          <t>General Lagos</t>
         </is>
       </c>
     </row>
